--- a/docs/test management/EspoCRM-Automation-Tracker.xlsx
+++ b/docs/test management/EspoCRM-Automation-Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SIDDIQ\EspoCRM-QA-Automation\docs\test management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB96A668-0DA9-44B6-A20F-9A649EC80E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C952DCE0-3F9C-4494-B836-CD609532B71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,25 @@
     <sheet name="Test Data Strategy" sheetId="4" r:id="rId4"/>
     <sheet name="Manual Cases" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="369">
   <si>
     <t>EspoCRM QA Automation — Accounts Module Tracker</t>
   </si>
@@ -83,7 +96,7 @@
     <t>Latest regression result</t>
   </si>
   <si>
-    <t>PASS — Component suites: Create 5/5, Duplicate 2/2, Delete 3/3</t>
+    <t>PASS — Full Accounts Regression: 19/19</t>
   </si>
   <si>
     <t>AccountDuplicateTest</t>
@@ -495,6 +508,18 @@
     <t>Verify Personal Data option is available</t>
   </si>
   <si>
+    <t>AccountsPersonalDataTest</t>
+  </si>
+  <si>
+    <t>verifyViewPersonalData</t>
+  </si>
+  <si>
+    <t>Existing Account – Test Account 003</t>
+  </si>
+  <si>
+    <t>View Personal Data dialog opened, account name verified, and dialog closed</t>
+  </si>
+  <si>
     <t>TC-ACC-021</t>
   </si>
   <si>
@@ -688,6 +713,12 @@
   </si>
   <si>
     <t>Delete confirmation, delete from list, and delete from details passed.</t>
+  </si>
+  <si>
+    <t>Full Accounts Regression</t>
+  </si>
+  <si>
+    <t>TC-ACC-020 added; full Accounts regression completed successfully with 19/19 tests passing.</t>
   </si>
   <si>
     <t>Scenario</t>
@@ -1230,8 +1261,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1301,10 +1332,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1314,21 +1342,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1372,7 +1401,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
+  <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
@@ -1403,6 +1432,11 @@
           <c:tx>
             <c:v>Count</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
           <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
@@ -1428,20 +1462,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CA87-4F94-A765-390CA3CAE296}"/>
+              <c16:uniqueId val="{00000000-6DCA-419D-A357-F4DEA07D2732}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1548,7 +1582,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -1771,124 +1805,124 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="15.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="7" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.35" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="27.6">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+    </row>
+    <row r="3" spans="1:8" ht="27.6" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>13</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>36</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>2</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="6">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="6">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="6">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="6">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>1</v>
       </c>
       <c r="F7" s="1"/>
@@ -1896,35 +1930,35 @@
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="11">
-        <v>0.41666666666666669</v>
+      <c r="B8" s="9">
+        <v>0.44444444444444442</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="6">
-        <v>2</v>
+      <c r="E8" s="5">
+        <v>3</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" ht="55.2">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:8" ht="55.2" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>2</v>
       </c>
       <c r="F9" s="1"/>
@@ -1935,11 +1969,11 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="6">
-        <v>19</v>
+      <c r="E10" s="5">
+        <v>18</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1973,1631 +2007,1631 @@
     <col min="14" max="14" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="27.6">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:14" ht="27.6" customHeight="1">
+      <c r="A1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="27.6">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:14" ht="27.6" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="I2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="27.6">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:14" ht="27.6" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="I3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="27.6">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:14" ht="27.6" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="I4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="27.6">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:14" ht="27.6" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="I5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="27.6">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:14" ht="27.6" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="I6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="N6" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="41.4">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="I7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="N7" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="110.4">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:14" ht="110.4" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="I8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="N8" s="5" t="s">
+      <c r="N8" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="27.6">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:14" ht="27.6" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="I9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="5" t="s">
+      <c r="N9" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="27.6">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:14" ht="27.6" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="I10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="N10" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="27.6">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:14" ht="27.6" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="I11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="N11" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="41.4">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="I12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="5" t="s">
+      <c r="L12" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="5" t="s">
+      <c r="N12" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="41.4">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="D13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" s="5" t="s">
+      <c r="I13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="L13" s="5" t="s">
+      <c r="L13" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="N13" s="5" t="s">
+      <c r="N13" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="41.4">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A14" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J14" s="5" t="s">
+      <c r="I14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="5" t="s">
+      <c r="L14" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="N14" s="5" t="s">
+      <c r="N14" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="41.4">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A15" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="D15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="5" t="s">
+      <c r="I15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="L15" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="M15" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="N15" s="5" t="s">
+      <c r="N15" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="41.4">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="D16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="I16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="L16" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N16" s="5" t="s">
+      <c r="N16" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="41.4">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A17" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="D17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="I17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L17" s="5" t="s">
+      <c r="L17" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="M17" s="5" t="s">
+      <c r="M17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="N17" s="5" t="s">
+      <c r="N17" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="41.4">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A18" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="D18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="5" t="s">
+      <c r="I18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L18" s="5" t="s">
+      <c r="L18" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="M18" s="5" t="s">
+      <c r="M18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="5" t="s">
+      <c r="N18" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="41.4">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A19" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="D19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="I19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L19" s="5" t="s">
+      <c r="L19" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="M19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N19" s="5" t="s">
+      <c r="N19" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="55.2">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:14" ht="55.2" customHeight="1">
+      <c r="A20" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="5" t="s">
+      <c r="D20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="5" t="s">
+      <c r="I20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L20" s="5" t="s">
+      <c r="L20" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="M20" s="5" t="s">
+      <c r="M20" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="N20" s="5" t="s">
+      <c r="N20" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="41.4">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="D21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J21" s="5" t="s">
+      <c r="I21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K22" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="L22" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M21" s="5" t="s">
+      <c r="M22" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N21" s="5" t="s">
+      <c r="N22" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="41.4">
-      <c r="A22" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="F22" s="5" t="s">
+    <row r="23" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="G23" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J22" s="5" t="s">
+      <c r="I23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K23" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="L23" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M22" s="5" t="s">
+      <c r="M23" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N22" s="5" t="s">
+      <c r="N23" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="41.4">
-      <c r="A23" s="5" t="s">
+    <row r="24" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="D24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="G24" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="I24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="K24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L23" s="5" t="s">
+      <c r="L24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M23" s="5" t="s">
+      <c r="M24" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N23" s="5" t="s">
+      <c r="N24" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="41.4">
-      <c r="A24" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="5" t="s">
+    <row r="25" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="H25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="G26" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="I26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="K26" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L24" s="5" t="s">
+      <c r="L26" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="M26" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N24" s="5" t="s">
+      <c r="N26" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="41.4">
-      <c r="A25" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F25" s="5" t="s">
+    <row r="27" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="G27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J25" s="5" t="s">
+      <c r="I27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="K27" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L25" s="5" t="s">
+      <c r="L27" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M25" s="5" t="s">
+      <c r="M27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N25" s="5" t="s">
+      <c r="N27" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="41.4">
-      <c r="A26" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F26" s="5" t="s">
+    <row r="28" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J26" s="5" t="s">
+      <c r="I31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J31" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="K31" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L26" s="5" t="s">
+      <c r="L31" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M26" s="5" t="s">
+      <c r="M31" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N26" s="5" t="s">
+      <c r="N31" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="41.4">
-      <c r="A27" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="F27" s="5" t="s">
+    <row r="32" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G32" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J27" s="5" t="s">
+      <c r="I35" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K35" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L27" s="5" t="s">
+      <c r="L35" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M27" s="5" t="s">
+      <c r="M35" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N27" s="5" t="s">
+      <c r="N35" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="41.4">
-      <c r="A28" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J28" s="5" t="s">
+    <row r="36" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J36" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="K36" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L28" s="5" t="s">
+      <c r="L36" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M28" s="5" t="s">
+      <c r="M36" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N28" s="5" t="s">
+      <c r="N36" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="41.4">
-      <c r="A29" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J29" s="5" t="s">
+    <row r="37" spans="1:14" ht="41.4" customHeight="1">
+      <c r="A37" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J37" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K29" s="5" t="s">
+      <c r="K37" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="L29" s="5" t="s">
+      <c r="L37" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M29" s="5" t="s">
+      <c r="M37" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N29" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="41.4">
-      <c r="A30" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N30" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="41.4">
-      <c r="A31" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N31" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="41.4">
-      <c r="A32" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N32" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="41.4">
-      <c r="A33" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N33" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="41.4">
-      <c r="A34" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N34" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="41.4">
-      <c r="A35" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N35" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="41.4">
-      <c r="A36" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N36" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="41.4">
-      <c r="A37" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N37" s="5" t="s">
+      <c r="N37" s="4" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3622,6 +3656,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3640,167 +3675,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="F1" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>46262</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="B2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="4">
         <v>7</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="4">
         <v>7</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="4">
         <v>7</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="4">
         <v>0</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>214</v>
+      <c r="I2" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="9">
+      <c r="A3" s="7">
         <v>46262</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="8">
         <v>5</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="8">
         <v>5</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="8">
         <v>5</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="8">
         <v>0</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="8">
         <v>0</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>215</v>
+      <c r="I3" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="9">
+      <c r="A4" s="7">
         <v>46262</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="8">
         <v>2</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>2</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="8">
         <v>2</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="8">
         <v>0</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <v>0</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>216</v>
+      <c r="I4" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="9">
+      <c r="A5" s="7">
         <v>46262</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>3</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>3</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="8">
         <v>3</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <v>0</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <v>0</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="J5" s="10" t="s">
+      <c r="I5" s="8" t="s">
         <v>217</v>
       </c>
+      <c r="J5" s="8" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="2"/>
+      <c r="A6" s="7">
+        <v>46280</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" s="8">
+        <v>19</v>
+      </c>
+      <c r="E6" s="8">
+        <v>19</v>
+      </c>
+      <c r="F6" s="8">
+        <v>19</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2"/>
@@ -4101,87 +4165,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="27.6">
-      <c r="A2" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="27.6">
-      <c r="A3" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C3" s="5" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="27.6">
-      <c r="A4" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C4" s="5" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="27.6">
-      <c r="A5" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C5" s="5" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>237</v>
       </c>
+      <c r="C4" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>241</v>
+      <c r="A6" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -4205,1515 +4269,1515 @@
     <col min="13" max="13" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="27.6">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:13" ht="27.6" customHeight="1">
+      <c r="A1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="27.6">
-      <c r="A2" s="5" t="s">
+      <c r="H1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="27.6" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="H2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="55.2">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="H3" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="27.6">
-      <c r="A4" s="5" t="s">
+      <c r="M3" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="27.6" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="H4" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="41.4">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:13" ht="41.4" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" s="5" t="s">
+      <c r="H5" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="55.2">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="H6" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="69">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:13" ht="69" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="H7" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="124.2">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:13" ht="124.2" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="H8" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="55.2">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="5" t="s">
+      <c r="H9" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="55.2">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="5" t="s">
+      <c r="H10" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M10" s="5"/>
-    </row>
-    <row r="11" spans="1:13" ht="82.8">
-      <c r="A11" s="5" t="s">
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" ht="82.8" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" s="5" t="s">
+      <c r="H11" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M11" s="5"/>
-    </row>
-    <row r="12" spans="1:13" ht="41.4">
-      <c r="A12" s="5" t="s">
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" ht="41.4" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="5" t="s">
+      <c r="H12" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M12" s="5"/>
-    </row>
-    <row r="13" spans="1:13" ht="41.4">
-      <c r="A13" s="5" t="s">
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" ht="41.4" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="D13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L13" s="5" t="s">
+      <c r="H13" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="69">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:13" ht="69" customHeight="1">
+      <c r="A14" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" s="5" t="s">
+      <c r="H14" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="55.2">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A15" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="D15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L15" s="5" t="s">
+      <c r="H15" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="M15" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="55.2">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="D16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L16" s="5" t="s">
+      <c r="H16" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="41.4">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:13" ht="41.4" customHeight="1">
+      <c r="A17" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="D17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L17" s="5" t="s">
+      <c r="H17" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M17" s="5" t="s">
+      <c r="M17" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="41.4">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:13" ht="41.4" customHeight="1">
+      <c r="A18" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="D18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H18" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="5" t="s">
+      <c r="H18" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M18" s="5" t="s">
+      <c r="M18" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="69">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:13" ht="69" customHeight="1">
+      <c r="A19" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="D19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L19" s="5" t="s">
+      <c r="H19" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="M19" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="55.2">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A20" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="5" t="s">
+      <c r="D20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L20" s="5" t="s">
+      <c r="H20" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M20" s="5" t="s">
+      <c r="M20" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="55.2">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="D21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L21" s="5" t="s">
+      <c r="H21" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M21" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="69">
-      <c r="A22" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="F22" s="5" t="s">
+      <c r="M21" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="69" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L22" s="5" t="s">
+      <c r="G22" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M22" s="5" t="s">
+      <c r="M22" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="55.2">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="D23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L23" s="5" t="s">
+      <c r="G23" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M23" s="5" t="s">
+      <c r="M23" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="55.2">
-      <c r="A24" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="5" t="s">
+    <row r="24" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="H24" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L24" s="5" t="s">
+      <c r="G25" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="M25" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="55.2">
-      <c r="A25" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F25" s="5" t="s">
+    <row r="26" spans="1:13" ht="69" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="I25" s="5" t="s">
+      <c r="G26" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="41.4" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="69" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="69" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="69" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="55.2" customHeight="1">
+      <c r="A37" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="I37" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="J25" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L25" s="5" t="s">
+      <c r="J37" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M25" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="69">
-      <c r="A26" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="55.2">
-      <c r="A27" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="55.2">
-      <c r="A28" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="41.4">
-      <c r="A29" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="69">
-      <c r="A30" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="69">
-      <c r="A31" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="69">
-      <c r="A32" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="55.2">
-      <c r="A33" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="55.2">
-      <c r="A34" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="55.2">
-      <c r="A35" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="55.2">
-      <c r="A36" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="55.2">
-      <c r="A37" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>362</v>
+      <c r="M37" s="4" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
